--- a/data/dividends_info_20260707.xlsx
+++ b/data/dividends_info_20260707.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>59.97999954223633</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1500500178173966</v>
+        <v>0.1543739299790388</v>
       </c>
       <c r="J2" t="n">
         <v>251</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.19999694824219</v>
+        <v>65.59999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.057401861434054</v>
+        <v>1.067073195552202</v>
       </c>
       <c r="J3" t="n">
         <v>230</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.619999885559082</v>
+        <v>9.920000076293945</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6237006311202571</v>
+        <v>0.6048387050256521</v>
       </c>
       <c r="J4" t="n">
         <v>160</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>59.93999862670898</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1501501535902545</v>
+        <v>0.1543739299790388</v>
       </c>
       <c r="J6" t="n">
         <v>160</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.130000114440918</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.615023279949961</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>139</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.59000015258789</v>
+        <v>20.5049991607666</v>
       </c>
       <c r="I8" t="n">
-        <v>1.311316163181595</v>
+        <v>1.316752065596797</v>
       </c>
       <c r="J8" t="n">
         <v>139</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.079999923706055</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>3.289473725487982</v>
+        <v>3.305785019747363</v>
       </c>
       <c r="J9" t="n">
         <v>132</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.699999809265137</v>
+        <v>7.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>104</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.940000057220459</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7723577116003624</v>
       </c>
       <c r="J13" t="n">
         <v>83</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.59000015258789</v>
+        <v>20.5049991607666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.311316163181595</v>
+        <v>1.316752065596797</v>
       </c>
       <c r="J14" t="n">
         <v>76</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>59.93999862670898</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1501501535902545</v>
+        <v>0.1543739299790388</v>
       </c>
       <c r="J15" t="n">
         <v>76</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.940000057220459</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7723577116003624</v>
       </c>
       <c r="J18" t="n">
         <v>27</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.789999961853027</v>
+        <v>5.769999980926514</v>
       </c>
       <c r="I19" t="n">
-        <v>4.317789320329981</v>
+        <v>4.33275564690481</v>
       </c>
       <c r="J19" t="n">
         <v>20</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.119999885559082</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I20" t="n">
-        <v>3.398058346814786</v>
+        <v>3.414634225767048</v>
       </c>
       <c r="J20" t="n">
         <v>13</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.21399974822998</v>
+        <v>10.13399982452393</v>
       </c>
       <c r="I21" t="n">
-        <v>2.545525811717944</v>
+        <v>2.56562072727502</v>
       </c>
       <c r="J21" t="n">
         <v>13</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.88000011444092</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="I22" t="n">
-        <v>4.032258033504347</v>
+        <v>4.10958893372029</v>
       </c>
       <c r="J22" t="n">
         <v>13</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.845999956130981</v>
+        <v>2.834000110626221</v>
       </c>
       <c r="I23" t="n">
-        <v>7.730147694699224</v>
+        <v>7.762879019485544</v>
       </c>
       <c r="J23" t="n">
         <v>13</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.985000133514404</v>
+        <v>6.929999828338623</v>
       </c>
       <c r="I25" t="n">
-        <v>1.431639199549827</v>
+        <v>1.443001478745689</v>
       </c>
       <c r="J25" t="n">
         <v>13</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.85000038146973</v>
+        <v>19.95000076293945</v>
       </c>
       <c r="I26" t="n">
-        <v>1.89420651271625</v>
+        <v>1.884711707372385</v>
       </c>
       <c r="J26" t="n">
         <v>13</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.829999923706055</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I27" t="n">
-        <v>2.058319066387184</v>
+        <v>2.061855609288493</v>
       </c>
       <c r="J27" t="n">
         <v>6</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.400000095367432</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="I29" t="n">
-        <v>4.411764582135689</v>
+        <v>4.518072380004178</v>
       </c>
       <c r="J29" t="n">
         <v>6</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.240000009536743</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I30" t="n">
-        <v>3.794642840987262</v>
+        <v>3.828828779484834</v>
       </c>
       <c r="J30" t="n">
         <v>-1</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.510000228881836</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I31" t="n">
-        <v>1.552106351386042</v>
+        <v>1.518438133897318</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36.79999923706055</v>
+        <v>36.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4076087041027381</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9.600000381469727</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I33" t="n">
-        <v>23.25937407575551</v>
+        <v>23.01958808150907</v>
       </c>
       <c r="J33" t="n">
         <v>-1</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>21.84000015258789</v>
+        <v>21.6200008392334</v>
       </c>
       <c r="I35" t="n">
-        <v>1.144688636691134</v>
+        <v>1.156336680368346</v>
       </c>
       <c r="J35" t="n">
         <v>-15</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>29.64999961853027</v>
+        <v>28.89999961853027</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6576728583771428</v>
+        <v>0.6747404933354004</v>
       </c>
       <c r="J36" t="n">
         <v>-15</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.919999957084656</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="I37" t="n">
-        <v>1.718750038417057</v>
+        <v>1.755319153388305</v>
       </c>
       <c r="J37" t="n">
         <v>-15</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.255000114440918</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="I38" t="n">
-        <v>5.518553638144938</v>
+        <v>5.555555778850955</v>
       </c>
       <c r="J38" t="n">
         <v>-15</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.818000078201294</v>
+        <v>3.803999900817871</v>
       </c>
       <c r="I39" t="n">
-        <v>4.190675660629582</v>
+        <v>4.20609895298892</v>
       </c>
       <c r="J39" t="n">
         <v>-15</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2.589999914169312</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I40" t="n">
-        <v>5.351351528691191</v>
+        <v>5.41406262101373</v>
       </c>
       <c r="J40" t="n">
         <v>-15</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>55.63000106811523</v>
+        <v>53.93000030517578</v>
       </c>
       <c r="I41" t="n">
-        <v>1.132482451741475</v>
+        <v>1.168180968727971</v>
       </c>
       <c r="J41" t="n">
         <v>-15</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6.320000171661377</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="I42" t="n">
-        <v>2.215189813249599</v>
+        <v>2.225755180430179</v>
       </c>
       <c r="J42" t="n">
         <v>-15</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>29.27000045776367</v>
+        <v>28.79000091552734</v>
       </c>
       <c r="I44" t="n">
-        <v>2.903997221409483</v>
+        <v>2.952413938762914</v>
       </c>
       <c r="J44" t="n">
         <v>-15</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>59.93999862670898</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1501501535902545</v>
+        <v>0.1543739299790388</v>
       </c>
       <c r="J45" t="n">
         <v>-15</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.379999995231628</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7246376836632911</v>
+        <v>0.7142857264499277</v>
       </c>
       <c r="J46" t="n">
         <v>-15</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>6.263999938964844</v>
+        <v>6.25</v>
       </c>
       <c r="I47" t="n">
-        <v>2.894316758725267</v>
+        <v>2.9008</v>
       </c>
       <c r="J47" t="n">
         <v>-15</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.770000457763672</v>
+        <v>9.779999732971191</v>
       </c>
       <c r="I48" t="n">
-        <v>2.661207654226798</v>
+        <v>2.658486780152613</v>
       </c>
       <c r="J48" t="n">
         <v>-15</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>10.20499992370605</v>
+        <v>10.23499965667725</v>
       </c>
       <c r="I49" t="n">
-        <v>2.714355728279168</v>
+        <v>2.706399699967621</v>
       </c>
       <c r="J49" t="n">
         <v>-15</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.179999947547913</v>
+        <v>1.184999942779541</v>
       </c>
       <c r="I50" t="n">
-        <v>1.14406784746504</v>
+        <v>1.139240561339973</v>
       </c>
       <c r="J50" t="n">
         <v>-22</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.002000093460083</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I51" t="n">
-        <v>3.664223736689323</v>
+        <v>3.691275144159233</v>
       </c>
       <c r="J51" t="n">
         <v>-22</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3.079999923706055</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="I53" t="n">
-        <v>5.194805323484478</v>
+        <v>5.245901721358718</v>
       </c>
       <c r="J53" t="n">
         <v>-29</v>
@@ -2990,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,7 +3115,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3142,14 +3142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3159,14 +3159,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3295,14 +3295,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3312,14 +3312,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3329,14 +3329,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3414,14 +3414,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3550,14 +3550,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3601,14 +3601,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3907,14 +3907,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4043,14 +4043,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4077,14 +4077,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4094,14 +4094,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4220,7 +4220,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4383,14 +4383,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4417,14 +4417,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4621,14 +4621,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4740,14 +4740,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4757,14 +4757,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5029,14 +5029,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5216,14 +5216,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5250,14 +5250,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5284,14 +5284,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5386,14 +5386,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5461,7 +5461,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5488,19 +5488,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5512,63 +5512,63 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5580,63 +5580,63 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5648,12 +5648,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5665,7 +5665,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5726,14 +5726,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5777,14 +5777,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5794,36 +5794,36 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5835,12 +5835,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5852,29 +5852,29 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5886,97 +5886,97 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5988,29 +5988,29 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6022,29 +6022,29 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6056,41 +6056,41 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6100,14 +6100,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6117,14 +6117,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6134,14 +6134,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6158,29 +6158,29 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6192,12 +6192,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6209,29 +6209,29 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6243,12 +6243,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6260,75 +6260,75 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6372,14 +6372,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6406,14 +6406,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6447,7 +6447,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6481,12 +6481,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6498,29 +6498,29 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6532,97 +6532,97 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6634,24 +6634,24 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6678,14 +6678,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6719,7 +6719,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6746,14 +6746,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6762,176 +6762,6 @@
         </is>
       </c>
       <c r="C222" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Abitare In S.p.A.</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
         <is>
           <t>Half Year Report</t>
         </is>
@@ -6961,350 +6791,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Abitare In S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GEFRAN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>doxee S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>